--- a/Scrape PHEI/2026-05-Mei/Yield-Curve-26-Mei-2026.xlsx
+++ b/Scrape PHEI/2026-05-Mei/Yield-Curve-26-Mei-2026.xlsx
@@ -585,7 +585,7 @@
         <v>0.06858599999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06902534049262798</v>
+        <v>0.06902534049262821</v>
       </c>
     </row>
     <row r="15">
@@ -618,7 +618,7 @@
         <v>0.068679</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06908071388563286</v>
+        <v>0.06908071388563264</v>
       </c>
     </row>
     <row r="18">
@@ -640,7 +640,7 @@
         <v>0.06869500000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06906126109961952</v>
+        <v>0.06906126109961974</v>
       </c>
     </row>
     <row r="20">
@@ -750,7 +750,7 @@
         <v>0.068702</v>
       </c>
       <c r="C29" t="n">
-        <v>0.06893745981119315</v>
+        <v>0.06893745981119292</v>
       </c>
     </row>
     <row r="30">
@@ -827,7 +827,7 @@
         <v>0.068702</v>
       </c>
       <c r="C36" t="n">
-        <v>0.06888897855078646</v>
+        <v>0.06888897855078624</v>
       </c>
     </row>
     <row r="37">
